--- a/data/datasets_produtos/itabuna/oleo_itabuna.xlsx
+++ b/data/datasets_produtos/itabuna/oleo_itabuna.xlsx
@@ -2934,6 +2934,14 @@
         <v>10.380000000000001</v>
       </c>
     </row>
+    <row r="254" ht="15.75" customHeight="1">
+      <c r="A254" s="4">
+        <v>46387</v>
+      </c>
+      <c r="B254">
+        <v>8.4000000000000004</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157500000008" bottom="0.78740157500000008" header="0.31496062000000014" footer="0.31496062000000014"/>

--- a/data/datasets_produtos/itabuna/oleo_itabuna.xlsx
+++ b/data/datasets_produtos/itabuna/oleo_itabuna.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
   <si>
     <t>ano</t>
   </si>
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t>31-11-2025</t>
+  </si>
+  <si>
+    <t>31-02-2026</t>
   </si>
 </sst>
 </file>
@@ -383,7 +386,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -392,6 +395,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2936,10 +2942,18 @@
     </row>
     <row r="254" ht="15.75" customHeight="1">
       <c r="A254" s="4">
-        <v>46387</v>
+        <v>46053</v>
       </c>
       <c r="B254">
         <v>8.4000000000000004</v>
+      </c>
+    </row>
+    <row r="255" ht="15.75" customHeight="1">
+      <c r="A255" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B255">
+        <v>8.3800000000000008</v>
       </c>
     </row>
   </sheetData>

--- a/data/datasets_produtos/itabuna/oleo_itabuna.xlsx
+++ b/data/datasets_produtos/itabuna/oleo_itabuna.xlsx
@@ -352,8 +352,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -398,9 +399,7 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2949,10 +2948,18 @@
       </c>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="A255" s="5" t="s">
+      <c r="A255" s="4" t="s">
         <v>109</v>
       </c>
       <c r="B255">
+        <v>8.3800000000000008</v>
+      </c>
+    </row>
+    <row r="256" ht="15.75" customHeight="1">
+      <c r="A256" s="5">
+        <v>46112</v>
+      </c>
+      <c r="B256">
         <v>8.3800000000000008</v>
       </c>
     </row>

--- a/data/datasets_produtos/itabuna/oleo_itabuna.xlsx
+++ b/data/datasets_produtos/itabuna/oleo_itabuna.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
   <si>
     <t>ano</t>
   </si>
@@ -346,6 +346,12 @@
   </si>
   <si>
     <t>31-02-2026</t>
+  </si>
+  <si>
+    <t>31-03-2026</t>
+  </si>
+  <si>
+    <t>31-04-2026</t>
   </si>
 </sst>
 </file>
@@ -399,7 +405,9 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2956,11 +2964,19 @@
       </c>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="A256" s="5">
-        <v>46112</v>
+      <c r="A256" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="B256">
         <v>8.3800000000000008</v>
+      </c>
+    </row>
+    <row r="257" ht="15.75" customHeight="1">
+      <c r="A257" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B257">
+        <v>8.5700000000000003</v>
       </c>
     </row>
   </sheetData>
